--- a/Data/child3.xlsx
+++ b/Data/child3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Farid\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\marmina\api\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB6A494-6DDC-41C1-9C38-952DA6E342C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C551BB2E-D9A6-4EED-AA6B-CAF83AFD187C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -1271,7 +1270,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1307,6 +1306,14 @@
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1363,7 +1370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1403,6 +1410,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1423,13 +1433,13 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
@@ -1836,9 +1846,9 @@
     <tableColumn id="9" xr3:uid="{FF8C4D30-2BF5-4E25-8F92-77C86FF95BE7}" name="joined_date" dataDxfId="7"/>
     <tableColumn id="10" xr3:uid="{A46008C8-FEF8-46AC-8566-65B3A105C4D5}" name="father" dataDxfId="6"/>
     <tableColumn id="1" xr3:uid="{318471C3-0537-4DDA-B106-B6B9F87E425E}" name="role" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{43F8C146-010B-46BD-B4F8-7B30F207E20C}" name="slogan" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{5263FFD1-4933-48E6-952A-CDFD1F0F6462}" name="family" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{CC11BC70-986C-4551-A616-E76D9AE15722}" name="stage" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{43F8C146-010B-46BD-B4F8-7B30F207E20C}" name="slogan" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{5263FFD1-4933-48E6-952A-CDFD1F0F6462}" name="family" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{CC11BC70-986C-4551-A616-E76D9AE15722}" name="stage" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2226,8 +2236,8 @@
       <c r="I2" s="7">
         <v>42162</v>
       </c>
-      <c r="J2" s="2">
-        <v>2024</v>
+      <c r="J2" s="15">
+        <v>45200</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="12" t="s">
@@ -2272,8 +2282,8 @@
       <c r="I3" s="7">
         <v>41969</v>
       </c>
-      <c r="J3" s="2">
-        <v>2024</v>
+      <c r="J3" s="15">
+        <v>45200</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>10</v>
@@ -2320,8 +2330,8 @@
       <c r="I4" s="7">
         <v>41640</v>
       </c>
-      <c r="J4" s="2">
-        <v>2024</v>
+      <c r="J4" s="15">
+        <v>45200</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>18</v>
@@ -2368,8 +2378,8 @@
       <c r="I5" s="7">
         <v>41903</v>
       </c>
-      <c r="J5" s="2">
-        <v>2024</v>
+      <c r="J5" s="15">
+        <v>45200</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="12" t="s">
@@ -2414,8 +2424,8 @@
       <c r="I6" s="7">
         <v>42280</v>
       </c>
-      <c r="J6" s="2">
-        <v>2024</v>
+      <c r="J6" s="15">
+        <v>45200</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>24</v>
@@ -2462,8 +2472,8 @@
       <c r="I7" s="7">
         <v>42278</v>
       </c>
-      <c r="J7" s="2">
-        <v>2024</v>
+      <c r="J7" s="15">
+        <v>45200</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="12" t="s">
@@ -2508,8 +2518,8 @@
       <c r="I8" s="7">
         <v>41160</v>
       </c>
-      <c r="J8" s="2">
-        <v>2024</v>
+      <c r="J8" s="15">
+        <v>45200</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>29</v>
@@ -2556,8 +2566,8 @@
       <c r="I9" s="7">
         <v>41094</v>
       </c>
-      <c r="J9" s="2">
-        <v>2024</v>
+      <c r="J9" s="15">
+        <v>45200</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>34</v>
@@ -2604,8 +2614,8 @@
       <c r="I10" s="7">
         <v>42241</v>
       </c>
-      <c r="J10" s="2">
-        <v>2024</v>
+      <c r="J10" s="15">
+        <v>45200</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>39</v>
@@ -2652,8 +2662,8 @@
       <c r="I11" s="7">
         <v>42388</v>
       </c>
-      <c r="J11" s="2">
-        <v>2024</v>
+      <c r="J11" s="15">
+        <v>45200</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>42</v>
@@ -2700,8 +2710,8 @@
       <c r="I12" s="7">
         <v>42203</v>
       </c>
-      <c r="J12" s="2">
-        <v>2024</v>
+      <c r="J12" s="15">
+        <v>45200</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="12" t="s">
@@ -2746,8 +2756,8 @@
       <c r="I13" s="7">
         <v>41738</v>
       </c>
-      <c r="J13" s="2">
-        <v>2024</v>
+      <c r="J13" s="15">
+        <v>45200</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>51</v>
@@ -2794,8 +2804,8 @@
       <c r="I14" s="7">
         <v>41944</v>
       </c>
-      <c r="J14" s="2">
-        <v>2024</v>
+      <c r="J14" s="15">
+        <v>45200</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>80</v>
@@ -2842,8 +2852,8 @@
       <c r="I15" s="7">
         <v>41675</v>
       </c>
-      <c r="J15" s="2">
-        <v>2024</v>
+      <c r="J15" s="15">
+        <v>45200</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>60</v>
@@ -2890,8 +2900,8 @@
       <c r="I16" s="7">
         <v>41791</v>
       </c>
-      <c r="J16" s="2">
-        <v>2024</v>
+      <c r="J16" s="15">
+        <v>45200</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>18</v>
@@ -2938,8 +2948,8 @@
       <c r="I17" s="7">
         <v>41859</v>
       </c>
-      <c r="J17" s="2">
-        <v>2024</v>
+      <c r="J17" s="15">
+        <v>45200</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>139</v>
@@ -2986,8 +2996,8 @@
       <c r="I18" s="7">
         <v>42169</v>
       </c>
-      <c r="J18" s="2">
-        <v>2024</v>
+      <c r="J18" s="15">
+        <v>45200</v>
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="12" t="s">
@@ -3032,8 +3042,8 @@
       <c r="I19" s="7">
         <v>41293</v>
       </c>
-      <c r="J19" s="2">
-        <v>2024</v>
+      <c r="J19" s="15">
+        <v>45200</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>18</v>
@@ -3080,8 +3090,8 @@
       <c r="I20" s="7">
         <v>40360</v>
       </c>
-      <c r="J20" s="2">
-        <v>2024</v>
+      <c r="J20" s="15">
+        <v>45200</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>266</v>
@@ -3128,8 +3138,8 @@
       <c r="I21" s="7">
         <v>41954</v>
       </c>
-      <c r="J21" s="2">
-        <v>2024</v>
+      <c r="J21" s="15">
+        <v>45200</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>80</v>
@@ -3176,8 +3186,8 @@
       <c r="I22" s="7">
         <v>41431</v>
       </c>
-      <c r="J22" s="2">
-        <v>2024</v>
+      <c r="J22" s="15">
+        <v>45200</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>24</v>
@@ -3224,8 +3234,8 @@
       <c r="I23" s="7">
         <v>48762</v>
       </c>
-      <c r="J23" s="2">
-        <v>2024</v>
+      <c r="J23" s="15">
+        <v>45200</v>
       </c>
       <c r="K23" s="8"/>
       <c r="L23" s="12" t="s">
@@ -3270,8 +3280,8 @@
       <c r="I24" s="7">
         <v>40829</v>
       </c>
-      <c r="J24" s="2">
-        <v>2024</v>
+      <c r="J24" s="15">
+        <v>45200</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>24</v>
@@ -3318,8 +3328,8 @@
       <c r="I25" s="7">
         <v>41301</v>
       </c>
-      <c r="J25" s="2">
-        <v>2024</v>
+      <c r="J25" s="15">
+        <v>45200</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="12" t="s">
@@ -3364,8 +3374,8 @@
       <c r="I26" s="7">
         <v>42135</v>
       </c>
-      <c r="J26" s="2">
-        <v>2024</v>
+      <c r="J26" s="15">
+        <v>45200</v>
       </c>
       <c r="K26" s="8"/>
       <c r="L26" s="12" t="s">
@@ -3410,8 +3420,8 @@
       <c r="I27" s="7">
         <v>42244</v>
       </c>
-      <c r="J27" s="2">
-        <v>2024</v>
+      <c r="J27" s="15">
+        <v>45200</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>18</v>
@@ -3458,8 +3468,8 @@
       <c r="I28" s="7">
         <v>41852</v>
       </c>
-      <c r="J28" s="2">
-        <v>2024</v>
+      <c r="J28" s="15">
+        <v>45200</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>24</v>
@@ -3506,8 +3516,8 @@
       <c r="I29" s="7">
         <v>42182</v>
       </c>
-      <c r="J29" s="2">
-        <v>2024</v>
+      <c r="J29" s="15">
+        <v>45200</v>
       </c>
       <c r="K29" s="8"/>
       <c r="L29" s="12" t="s">
@@ -3552,8 +3562,8 @@
       <c r="I30" s="7">
         <v>41190</v>
       </c>
-      <c r="J30" s="2">
-        <v>2024</v>
+      <c r="J30" s="15">
+        <v>45200</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>80</v>
@@ -3600,8 +3610,8 @@
       <c r="I31" s="7">
         <v>41590</v>
       </c>
-      <c r="J31" s="2">
-        <v>2024</v>
+      <c r="J31" s="15">
+        <v>45200</v>
       </c>
       <c r="K31" s="8"/>
       <c r="L31" s="12" t="s">
@@ -3646,8 +3656,8 @@
       <c r="I32" s="7">
         <v>41849</v>
       </c>
-      <c r="J32" s="2">
-        <v>2024</v>
+      <c r="J32" s="15">
+        <v>45200</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="12" t="s">
@@ -3692,8 +3702,8 @@
       <c r="I33" s="7">
         <v>41669</v>
       </c>
-      <c r="J33" s="2">
-        <v>2024</v>
+      <c r="J33" s="15">
+        <v>45200</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>116</v>
@@ -3740,8 +3750,8 @@
       <c r="I34" s="7">
         <v>42855</v>
       </c>
-      <c r="J34" s="2">
-        <v>2024</v>
+      <c r="J34" s="15">
+        <v>45200</v>
       </c>
       <c r="K34" s="8"/>
       <c r="L34" s="12" t="s">
@@ -3786,8 +3796,8 @@
       <c r="I35" s="7">
         <v>40782</v>
       </c>
-      <c r="J35" s="2">
-        <v>2024</v>
+      <c r="J35" s="15">
+        <v>45200</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>122</v>
@@ -3834,8 +3844,8 @@
       <c r="I36" s="7">
         <v>42669</v>
       </c>
-      <c r="J36" s="2">
-        <v>2024</v>
+      <c r="J36" s="15">
+        <v>45200</v>
       </c>
       <c r="K36" s="8"/>
       <c r="L36" s="12" t="s">
@@ -3880,8 +3890,8 @@
       <c r="I37" s="7">
         <v>40696</v>
       </c>
-      <c r="J37" s="2">
-        <v>2024</v>
+      <c r="J37" s="15">
+        <v>45200</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>129</v>
@@ -3928,8 +3938,8 @@
       <c r="I38" s="7">
         <v>42016</v>
       </c>
-      <c r="J38" s="2">
-        <v>2024</v>
+      <c r="J38" s="15">
+        <v>45200</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>265</v>
@@ -3976,8 +3986,8 @@
       <c r="I39" s="7">
         <v>42216</v>
       </c>
-      <c r="J39" s="2">
-        <v>2024</v>
+      <c r="J39" s="15">
+        <v>45200</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>24</v>
@@ -4024,8 +4034,8 @@
       <c r="I40" s="7">
         <v>41656</v>
       </c>
-      <c r="J40" s="2">
-        <v>2024</v>
+      <c r="J40" s="15">
+        <v>45200</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>139</v>
@@ -4072,8 +4082,8 @@
       <c r="I41" s="7">
         <v>42158</v>
       </c>
-      <c r="J41" s="2">
-        <v>2024</v>
+      <c r="J41" s="15">
+        <v>45200</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>139</v>
@@ -4120,8 +4130,8 @@
       <c r="I42" s="7">
         <v>41672</v>
       </c>
-      <c r="J42" s="2">
-        <v>2024</v>
+      <c r="J42" s="15">
+        <v>45200</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>80</v>
@@ -4168,8 +4178,8 @@
       <c r="I43" s="7">
         <v>42055</v>
       </c>
-      <c r="J43" s="2">
-        <v>2024</v>
+      <c r="J43" s="15">
+        <v>45200</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>264</v>
@@ -4216,8 +4226,8 @@
       <c r="I44" s="7">
         <v>42003</v>
       </c>
-      <c r="J44" s="2">
-        <v>2024</v>
+      <c r="J44" s="15">
+        <v>45200</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>24</v>
@@ -4264,8 +4274,8 @@
       <c r="I45" s="7">
         <v>42003</v>
       </c>
-      <c r="J45" s="2">
-        <v>2024</v>
+      <c r="J45" s="15">
+        <v>45200</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>122</v>
@@ -4312,8 +4322,8 @@
       <c r="I46" s="7">
         <v>41959</v>
       </c>
-      <c r="J46" s="2">
-        <v>2024</v>
+      <c r="J46" s="15">
+        <v>45200</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>156</v>
@@ -4360,8 +4370,8 @@
       <c r="I47" s="7">
         <v>40807</v>
       </c>
-      <c r="J47" s="2">
-        <v>2024</v>
+      <c r="J47" s="15">
+        <v>45200</v>
       </c>
       <c r="K47" s="8"/>
       <c r="L47" s="12" t="s">
@@ -4406,8 +4416,8 @@
       <c r="I48" s="7">
         <v>42184</v>
       </c>
-      <c r="J48" s="2">
-        <v>2024</v>
+      <c r="J48" s="15">
+        <v>45200</v>
       </c>
       <c r="K48" s="8"/>
       <c r="L48" s="12" t="s">
@@ -4452,8 +4462,8 @@
       <c r="I49" s="7">
         <v>41429</v>
       </c>
-      <c r="J49" s="2">
-        <v>2024</v>
+      <c r="J49" s="15">
+        <v>45200</v>
       </c>
       <c r="K49" s="8"/>
       <c r="L49" s="12" t="s">
@@ -4498,8 +4508,8 @@
       <c r="I50" s="7">
         <v>42292</v>
       </c>
-      <c r="J50" s="2">
-        <v>2024</v>
+      <c r="J50" s="15">
+        <v>45200</v>
       </c>
       <c r="K50" s="8"/>
       <c r="L50" s="12" t="s">
@@ -4544,8 +4554,8 @@
       <c r="I51" s="7">
         <v>42140</v>
       </c>
-      <c r="J51" s="2">
-        <v>2024</v>
+      <c r="J51" s="15">
+        <v>45200</v>
       </c>
       <c r="K51" s="8"/>
       <c r="L51" s="12" t="s">
@@ -4590,8 +4600,8 @@
       <c r="I52" s="7">
         <v>41978</v>
       </c>
-      <c r="J52" s="2">
-        <v>2024</v>
+      <c r="J52" s="15">
+        <v>45200</v>
       </c>
       <c r="K52" s="8"/>
       <c r="L52" s="12" t="s">
@@ -4636,8 +4646,8 @@
       <c r="I53" s="7">
         <v>41625</v>
       </c>
-      <c r="J53" s="2">
-        <v>2024</v>
+      <c r="J53" s="15">
+        <v>45200</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>15</v>
@@ -4684,8 +4694,8 @@
       <c r="I54" s="7">
         <v>41840</v>
       </c>
-      <c r="J54" s="2">
-        <v>2024</v>
+      <c r="J54" s="15">
+        <v>45200</v>
       </c>
       <c r="K54" s="8"/>
       <c r="L54" s="12" t="s">
@@ -4730,8 +4740,8 @@
       <c r="I55" s="7">
         <v>41852</v>
       </c>
-      <c r="J55" s="2">
-        <v>2024</v>
+      <c r="J55" s="15">
+        <v>45200</v>
       </c>
       <c r="K55" s="8"/>
       <c r="L55" s="12" t="s">
@@ -4776,8 +4786,8 @@
       <c r="I56" s="7">
         <v>42053</v>
       </c>
-      <c r="J56" s="2">
-        <v>2024</v>
+      <c r="J56" s="15">
+        <v>45200</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>80</v>
@@ -4824,8 +4834,8 @@
       <c r="I57" s="7">
         <v>41650</v>
       </c>
-      <c r="J57" s="2">
-        <v>2024</v>
+      <c r="J57" s="15">
+        <v>45200</v>
       </c>
       <c r="K57" s="8"/>
       <c r="L57" s="12" t="s">
@@ -4870,8 +4880,8 @@
       <c r="I58" s="7">
         <v>41290</v>
       </c>
-      <c r="J58" s="2">
-        <v>2024</v>
+      <c r="J58" s="15">
+        <v>45200</v>
       </c>
       <c r="K58" s="8"/>
       <c r="L58" s="12" t="s">
@@ -4916,8 +4926,8 @@
       <c r="I59" s="7">
         <v>40696</v>
       </c>
-      <c r="J59" s="2">
-        <v>2024</v>
+      <c r="J59" s="15">
+        <v>45200</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>202</v>
@@ -4964,8 +4974,8 @@
       <c r="I60" s="7">
         <v>40947</v>
       </c>
-      <c r="J60" s="2">
-        <v>2024</v>
+      <c r="J60" s="15">
+        <v>45200</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>39</v>
@@ -5012,8 +5022,8 @@
       <c r="I61" s="7">
         <v>41581</v>
       </c>
-      <c r="J61" s="2">
-        <v>2024</v>
+      <c r="J61" s="15">
+        <v>45200</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>209</v>
@@ -5060,8 +5070,8 @@
       <c r="I62" s="7">
         <v>41853</v>
       </c>
-      <c r="J62" s="2">
-        <v>2024</v>
+      <c r="J62" s="15">
+        <v>45200</v>
       </c>
       <c r="K62" s="8"/>
       <c r="L62" s="12" t="s">
@@ -5106,8 +5116,8 @@
       <c r="I63" s="7">
         <v>41881</v>
       </c>
-      <c r="J63" s="2">
-        <v>2024</v>
+      <c r="J63" s="15">
+        <v>45200</v>
       </c>
       <c r="K63" s="8"/>
       <c r="L63" s="12" t="s">
@@ -5152,8 +5162,8 @@
       <c r="I64" s="7">
         <v>41848</v>
       </c>
-      <c r="J64" s="2">
-        <v>2024</v>
+      <c r="J64" s="15">
+        <v>45200</v>
       </c>
       <c r="K64" s="8"/>
       <c r="L64" s="12" t="s">
@@ -5198,8 +5208,8 @@
       <c r="I65" s="7">
         <v>42156</v>
       </c>
-      <c r="J65" s="2">
-        <v>2024</v>
+      <c r="J65" s="15">
+        <v>45200</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>222</v>
@@ -5246,8 +5256,8 @@
       <c r="I66" s="7">
         <v>41893</v>
       </c>
-      <c r="J66" s="2">
-        <v>2024</v>
+      <c r="J66" s="15">
+        <v>45200</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>226</v>
@@ -5294,8 +5304,8 @@
       <c r="I67" s="7">
         <v>42096</v>
       </c>
-      <c r="J67" s="2">
-        <v>2024</v>
+      <c r="J67" s="15">
+        <v>45200</v>
       </c>
       <c r="K67" s="8"/>
       <c r="L67" s="12" t="s">
@@ -5340,8 +5350,8 @@
       <c r="I68" s="7">
         <v>42064</v>
       </c>
-      <c r="J68" s="2">
-        <v>2024</v>
+      <c r="J68" s="15">
+        <v>45200</v>
       </c>
       <c r="K68" s="8"/>
       <c r="L68" s="12" t="s">
@@ -5386,8 +5396,8 @@
       <c r="I69" s="7">
         <v>41395</v>
       </c>
-      <c r="J69" s="2">
-        <v>2024</v>
+      <c r="J69" s="15">
+        <v>45200</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>24</v>
@@ -5434,8 +5444,8 @@
       <c r="I70" s="7">
         <v>41467</v>
       </c>
-      <c r="J70" s="2">
-        <v>2024</v>
+      <c r="J70" s="15">
+        <v>45200</v>
       </c>
       <c r="K70" s="8"/>
       <c r="L70" s="12" t="s">
@@ -5480,8 +5490,8 @@
       <c r="I71" s="7">
         <v>41842</v>
       </c>
-      <c r="J71" s="2">
-        <v>2024</v>
+      <c r="J71" s="15">
+        <v>45200</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>245</v>
@@ -5528,8 +5538,8 @@
       <c r="I72" s="7">
         <v>41902</v>
       </c>
-      <c r="J72" s="2">
-        <v>2024</v>
+      <c r="J72" s="15">
+        <v>45200</v>
       </c>
       <c r="K72" s="8"/>
       <c r="L72" s="12" t="s">
@@ -5574,8 +5584,8 @@
       <c r="I73" s="7">
         <v>42046</v>
       </c>
-      <c r="J73" s="2">
-        <v>2024</v>
+      <c r="J73" s="15">
+        <v>45200</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>80</v>
@@ -5622,8 +5632,8 @@
       <c r="I74" s="7">
         <v>41301</v>
       </c>
-      <c r="J74" s="2">
-        <v>2024</v>
+      <c r="J74" s="15">
+        <v>45200</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>80</v>
@@ -5670,8 +5680,8 @@
       <c r="I75" s="7">
         <v>41485</v>
       </c>
-      <c r="J75" s="2">
-        <v>2024</v>
+      <c r="J75" s="15">
+        <v>45200</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>264</v>
@@ -5718,8 +5728,8 @@
       <c r="I76" s="7">
         <v>40973</v>
       </c>
-      <c r="J76" s="2">
-        <v>2024</v>
+      <c r="J76" s="15">
+        <v>45200</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>264</v>
@@ -5766,8 +5776,8 @@
       <c r="I77" s="7">
         <v>41964</v>
       </c>
-      <c r="J77" s="2">
-        <v>2024</v>
+      <c r="J77" s="15">
+        <v>45200</v>
       </c>
       <c r="K77" s="8"/>
       <c r="L77" s="12" t="s">
@@ -5812,8 +5822,8 @@
       <c r="I78" s="7">
         <v>41935</v>
       </c>
-      <c r="J78" s="2">
-        <v>2024</v>
+      <c r="J78" s="15">
+        <v>45200</v>
       </c>
       <c r="K78" s="8"/>
       <c r="L78" s="12" t="s">
@@ -5858,8 +5868,8 @@
       <c r="I79" s="7">
         <v>41827</v>
       </c>
-      <c r="J79" s="2">
-        <v>2024</v>
+      <c r="J79" s="15">
+        <v>45200</v>
       </c>
       <c r="K79" s="8"/>
       <c r="L79" s="12" t="s">
@@ -5904,8 +5914,8 @@
       <c r="I80" s="7">
         <v>42388</v>
       </c>
-      <c r="J80" s="2">
-        <v>2024</v>
+      <c r="J80" s="15">
+        <v>45200</v>
       </c>
       <c r="K80" s="8"/>
       <c r="L80" s="12" t="s">
@@ -5950,8 +5960,8 @@
       <c r="I81" s="7">
         <v>41939</v>
       </c>
-      <c r="J81" s="2">
-        <v>2024</v>
+      <c r="J81" s="15">
+        <v>45200</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>209</v>
@@ -5998,8 +6008,8 @@
       <c r="I82" s="7">
         <v>41757</v>
       </c>
-      <c r="J82" s="2">
-        <v>2024</v>
+      <c r="J82" s="15">
+        <v>45200</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>279</v>
@@ -6284,11 +6294,11 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="C25">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C26:C1048576 C2:C24">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C25">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
